--- a/site/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,336 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>h_01JZW9E9B6ZZRTWQSYHXT2DAAF</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/#h_01JZW9E9B6ZZRTWQSYHXT2DAAF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/#h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01KTNFWDZ7ZAP3S6NTF9SCCMC2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/#h_01KTNFWDZ7ZAP3S6NTF9SCCMC2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ADP Workforce Now</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01KRZNSHPKFRTMY95CGTCRTVG1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/#h_01KRZNSHPKFRTMY95CGTCRTVG1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ADP Workforce Now Objects</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01KRZP61CF0FRZKV5SMH9Z9364</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/#h_01KRZP61CF0FRZKV5SMH9Z9364</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Workers</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01KRZP9VZD2WGF8CRNXCYMM93H</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/#h_01KRZP9VZD2WGF8CRNXCYMM93H</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Azure Synapse</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KTNMG9VPSQYMVY1ABTAAJJPH</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/#h_01KTNMG9VPSQYMVY1ABTAAJJPH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KTNRFPX5KTDFPW5GZ4Z7084B</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/#h_01KTNRFPX5KTDFPW5GZ4Z7084B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Operational Settings</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Notification</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KTNSDH2WXFVQBZN2705QJQBM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/#h_01KTNSDH2WXFVQBZN2705QJQBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Email Notification</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KFDPWRK3JBR0HV1SHVH6ZA32</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/#h_01KFDPWRK3JBR0HV1SHVH6ZA32</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Azure-Synapse-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
